--- a/Output/Tables/tenure_share_tables.xlsx
+++ b/Output/Tables/tenure_share_tables.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="219">
   <si>
     <t>Country</t>
   </si>
@@ -36,28 +36,31 @@
     <t>Has certificate</t>
   </si>
   <si>
-    <t>Ethiopia</t>
-  </si>
-  <si>
-    <t>Malawi</t>
-  </si>
-  <si>
-    <t>Mali</t>
-  </si>
-  <si>
-    <t>Niger</t>
-  </si>
-  <si>
-    <t>Nigeria</t>
-  </si>
-  <si>
-    <t>Tanzania</t>
-  </si>
-  <si>
-    <t>Uganda</t>
-  </si>
-  <si>
-    <t>Zambia</t>
+    <t>Ethiopia (LSMS)</t>
+  </si>
+  <si>
+    <t>Malawi (LSMS)</t>
+  </si>
+  <si>
+    <t>Mali (LSMS)</t>
+  </si>
+  <si>
+    <t>Niger (LSMS)</t>
+  </si>
+  <si>
+    <t>Nigeria (LSMS)</t>
+  </si>
+  <si>
+    <t>Tanzania (LSMS)</t>
+  </si>
+  <si>
+    <t>Tanzania (ASC)</t>
+  </si>
+  <si>
+    <t>Uganda (LSMS)</t>
+  </si>
+  <si>
+    <t>Zambia (RALS)</t>
   </si>
   <si>
     <t>2012</t>
@@ -78,15 +81,15 @@
     <t>2010</t>
   </si>
   <si>
+    <t>2017</t>
+  </si>
+  <si>
+    <t>2011</t>
+  </si>
+  <si>
     <t>2013</t>
   </si>
   <si>
-    <t>2017</t>
-  </si>
-  <si>
-    <t>2011</t>
-  </si>
-  <si>
     <t>2023</t>
   </si>
   <si>
@@ -114,460 +117,475 @@
     <t>0.234</t>
   </si>
   <si>
-    <t>0.121</t>
+    <t>0.101</t>
+  </si>
+  <si>
+    <t>0.096</t>
+  </si>
+  <si>
+    <t>0.100</t>
+  </si>
+  <si>
+    <t>0.030</t>
+  </si>
+  <si>
+    <t>0.010</t>
+  </si>
+  <si>
+    <t>0.232</t>
+  </si>
+  <si>
+    <t>0.038</t>
+  </si>
+  <si>
+    <t>0.103</t>
+  </si>
+  <si>
+    <t>0.104</t>
+  </si>
+  <si>
+    <t>0.090</t>
+  </si>
+  <si>
+    <t>0.187</t>
+  </si>
+  <si>
+    <t>0.145</t>
+  </si>
+  <si>
+    <t>0.112</t>
+  </si>
+  <si>
+    <t>0.075</t>
+  </si>
+  <si>
+    <t>0.061</t>
+  </si>
+  <si>
+    <t>0.093</t>
+  </si>
+  <si>
+    <t>0.152</t>
+  </si>
+  <si>
+    <t>0.108</t>
+  </si>
+  <si>
+    <t>0.201</t>
+  </si>
+  <si>
+    <t>0.214</t>
+  </si>
+  <si>
+    <t>0.202</t>
+  </si>
+  <si>
+    <t>0.136</t>
+  </si>
+  <si>
+    <t>0.172</t>
+  </si>
+  <si>
+    <t>0.210</t>
+  </si>
+  <si>
+    <t>0.188</t>
+  </si>
+  <si>
+    <t>0.045</t>
+  </si>
+  <si>
+    <t>0.073</t>
+  </si>
+  <si>
+    <t>0.132</t>
+  </si>
+  <si>
+    <t>0.178</t>
   </si>
   <si>
     <t>0.117</t>
   </si>
   <si>
+    <t>0.050</t>
+  </si>
+  <si>
+    <t>0.001</t>
+  </si>
+  <si>
+    <t>0.013</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>0.005</t>
+  </si>
+  <si>
+    <t>0.002</t>
+  </si>
+  <si>
+    <t>0.006</t>
+  </si>
+  <si>
+    <t>0.019</t>
+  </si>
+  <si>
+    <t>0.012</t>
+  </si>
+  <si>
+    <t>0.029</t>
+  </si>
+  <si>
+    <t>0.028</t>
+  </si>
+  <si>
+    <t>0.004</t>
+  </si>
+  <si>
+    <t>0.011</t>
+  </si>
+  <si>
+    <t>0.023</t>
+  </si>
+  <si>
+    <t>0.024</t>
+  </si>
+  <si>
+    <t>0.018</t>
+  </si>
+  <si>
+    <t>0.099</t>
+  </si>
+  <si>
+    <t>0.068</t>
+  </si>
+  <si>
+    <t>0.082</t>
+  </si>
+  <si>
+    <t>0.032</t>
+  </si>
+  <si>
+    <t>0.043</t>
+  </si>
+  <si>
+    <t>0.008</t>
+  </si>
+  <si>
+    <t>0.141</t>
+  </si>
+  <si>
+    <t>0.149</t>
+  </si>
+  <si>
+    <t>0.097</t>
+  </si>
+  <si>
+    <t>0.071</t>
+  </si>
+  <si>
+    <t>0.088</t>
+  </si>
+  <si>
+    <t>0.243</t>
+  </si>
+  <si>
+    <t>0.115</t>
+  </si>
+  <si>
+    <t>0.288</t>
+  </si>
+  <si>
+    <t>0.432</t>
+  </si>
+  <si>
+    <t>0.195</t>
+  </si>
+  <si>
+    <t>0.077</t>
+  </si>
+  <si>
+    <t>0.379</t>
+  </si>
+  <si>
+    <t>0.350</t>
+  </si>
+  <si>
+    <t>0.298</t>
+  </si>
+  <si>
+    <t>0.352</t>
+  </si>
+  <si>
+    <t>0.366</t>
+  </si>
+  <si>
+    <t>0.346</t>
+  </si>
+  <si>
+    <t>0.056</t>
+  </si>
+  <si>
+    <t>0.079</t>
+  </si>
+  <si>
+    <t>0.486</t>
+  </si>
+  <si>
+    <t>0.537</t>
+  </si>
+  <si>
+    <t>0.586</t>
+  </si>
+  <si>
+    <t>0.790</t>
+  </si>
+  <si>
+    <t>0.782</t>
+  </si>
+  <si>
+    <t>0.063</t>
+  </si>
+  <si>
+    <t>0.126</t>
+  </si>
+  <si>
+    <t>0.055</t>
+  </si>
+  <si>
+    <t>0.109</t>
+  </si>
+  <si>
+    <t>0.174</t>
+  </si>
+  <si>
+    <t>0.130</t>
+  </si>
+  <si>
+    <t>0.144</t>
+  </si>
+  <si>
+    <t>0.116</t>
+  </si>
+  <si>
+    <t>0.146</t>
+  </si>
+  <si>
+    <t>0.218</t>
+  </si>
+  <si>
+    <t>0.226</t>
+  </si>
+  <si>
+    <t>0.168</t>
+  </si>
+  <si>
+    <t>0.159</t>
+  </si>
+  <si>
+    <t>0.256</t>
+  </si>
+  <si>
+    <t>0.127</t>
+  </si>
+  <si>
+    <t>0.086</t>
+  </si>
+  <si>
+    <t>0.054</t>
+  </si>
+  <si>
+    <t>0.111</t>
+  </si>
+  <si>
+    <t>0.134</t>
+  </si>
+  <si>
+    <t>0.080</t>
+  </si>
+  <si>
+    <t>0.074</t>
+  </si>
+  <si>
+    <t>0.143</t>
+  </si>
+  <si>
+    <t>0.062</t>
+  </si>
+  <si>
+    <t>0.042</t>
+  </si>
+  <si>
     <t>0.119</t>
   </si>
   <si>
-    <t>0.109</t>
-  </si>
-  <si>
-    <t>0.030</t>
-  </si>
-  <si>
-    <t>0.010</t>
-  </si>
-  <si>
-    <t>0.232</t>
-  </si>
-  <si>
-    <t>0.038</t>
-  </si>
-  <si>
-    <t>0.103</t>
-  </si>
-  <si>
-    <t>0.104</t>
-  </si>
-  <si>
-    <t>0.090</t>
-  </si>
-  <si>
-    <t>0.187</t>
-  </si>
-  <si>
-    <t>0.145</t>
-  </si>
-  <si>
-    <t>0.112</t>
-  </si>
-  <si>
-    <t>0.075</t>
-  </si>
-  <si>
-    <t>0.061</t>
-  </si>
-  <si>
-    <t>0.093</t>
-  </si>
-  <si>
-    <t>0.152</t>
-  </si>
-  <si>
-    <t>0.214</t>
-  </si>
-  <si>
-    <t>0.202</t>
-  </si>
-  <si>
-    <t>0.136</t>
-  </si>
-  <si>
-    <t>0.172</t>
-  </si>
-  <si>
-    <t>0.210</t>
-  </si>
-  <si>
-    <t>0.188</t>
-  </si>
-  <si>
-    <t>0.045</t>
-  </si>
-  <si>
-    <t>0.073</t>
-  </si>
-  <si>
-    <t>0.132</t>
-  </si>
-  <si>
-    <t>0.178</t>
-  </si>
-  <si>
-    <t>0.050</t>
-  </si>
-  <si>
-    <t>0.004</t>
-  </si>
-  <si>
-    <t>0.006</t>
-  </si>
-  <si>
-    <t>0.024</t>
-  </si>
-  <si>
-    <t>0.023</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>0.001</t>
-  </si>
-  <si>
-    <t>0.005</t>
-  </si>
-  <si>
-    <t>0.002</t>
-  </si>
-  <si>
-    <t>0.019</t>
-  </si>
-  <si>
-    <t>0.013</t>
-  </si>
-  <si>
-    <t>0.012</t>
-  </si>
-  <si>
-    <t>0.029</t>
-  </si>
-  <si>
-    <t>0.011</t>
-  </si>
-  <si>
-    <t>0.018</t>
-  </si>
-  <si>
-    <t>0.099</t>
-  </si>
-  <si>
-    <t>0.068</t>
-  </si>
-  <si>
-    <t>0.082</t>
+    <t>0.085</t>
+  </si>
+  <si>
+    <t>0.106</t>
+  </si>
+  <si>
+    <t>0.139</t>
+  </si>
+  <si>
+    <t>0.128</t>
+  </si>
+  <si>
+    <t>0.016</t>
+  </si>
+  <si>
+    <t>0.017</t>
+  </si>
+  <si>
+    <t>0.053</t>
+  </si>
+  <si>
+    <t>0.064</t>
+  </si>
+  <si>
+    <t>0.022</t>
+  </si>
+  <si>
+    <t>0.000</t>
+  </si>
+  <si>
+    <t>0.007</t>
+  </si>
+  <si>
+    <t>0.014</t>
+  </si>
+  <si>
+    <t>0.003</t>
+  </si>
+  <si>
+    <t>0.040</t>
+  </si>
+  <si>
+    <t>0.033</t>
+  </si>
+  <si>
+    <t>0.035</t>
+  </si>
+  <si>
+    <t>0.036</t>
+  </si>
+  <si>
+    <t>0.098</t>
+  </si>
+  <si>
+    <t>0.069</t>
+  </si>
+  <si>
+    <t>0.131</t>
+  </si>
+  <si>
+    <t>0.072</t>
+  </si>
+  <si>
+    <t>0.247</t>
+  </si>
+  <si>
+    <t>0.265</t>
+  </si>
+  <si>
+    <t>0.211</t>
+  </si>
+  <si>
+    <t>0.253</t>
+  </si>
+  <si>
+    <t>0.254</t>
+  </si>
+  <si>
+    <t>0.047</t>
+  </si>
+  <si>
+    <t>0.057</t>
+  </si>
+  <si>
+    <t>0.458</t>
+  </si>
+  <si>
+    <t>0.510</t>
+  </si>
+  <si>
+    <t>0.555</t>
+  </si>
+  <si>
+    <t>0.717</t>
+  </si>
+  <si>
+    <t>0.688</t>
+  </si>
+  <si>
+    <t>0.041</t>
+  </si>
+  <si>
+    <t>0.031</t>
+  </si>
+  <si>
+    <t>0.095</t>
+  </si>
+  <si>
+    <t>0.070</t>
+  </si>
+  <si>
+    <t>0.110</t>
+  </si>
+  <si>
+    <t>0.157</t>
+  </si>
+  <si>
+    <t>0.105</t>
+  </si>
+  <si>
+    <t>0.186</t>
+  </si>
+  <si>
+    <t>0.151</t>
+  </si>
+  <si>
+    <t>0.091</t>
+  </si>
+  <si>
+    <t>0.192</t>
+  </si>
+  <si>
+    <t>0.164</t>
   </si>
   <si>
     <t>0.039</t>
   </si>
   <si>
-    <t>0.031</t>
-  </si>
-  <si>
-    <t>0.065</t>
-  </si>
-  <si>
-    <t>0.008</t>
-  </si>
-  <si>
-    <t>0.141</t>
-  </si>
-  <si>
-    <t>0.149</t>
-  </si>
-  <si>
-    <t>0.097</t>
-  </si>
-  <si>
-    <t>0.071</t>
-  </si>
-  <si>
-    <t>0.088</t>
-  </si>
-  <si>
-    <t>0.243</t>
-  </si>
-  <si>
-    <t>0.115</t>
-  </si>
-  <si>
-    <t>0.288</t>
-  </si>
-  <si>
-    <t>0.432</t>
-  </si>
-  <si>
-    <t>0.379</t>
-  </si>
-  <si>
-    <t>0.350</t>
-  </si>
-  <si>
-    <t>0.298</t>
-  </si>
-  <si>
-    <t>0.352</t>
-  </si>
-  <si>
-    <t>0.366</t>
-  </si>
-  <si>
-    <t>0.346</t>
-  </si>
-  <si>
-    <t>0.056</t>
-  </si>
-  <si>
-    <t>0.079</t>
-  </si>
-  <si>
-    <t>0.486</t>
-  </si>
-  <si>
-    <t>0.537</t>
-  </si>
-  <si>
-    <t>0.586</t>
-  </si>
-  <si>
-    <t>0.790</t>
-  </si>
-  <si>
-    <t>0.782</t>
-  </si>
-  <si>
     <t>0.026</t>
   </si>
   <si>
-    <t>0.063</t>
-  </si>
-  <si>
-    <t>0.126</t>
-  </si>
-  <si>
-    <t>0.055</t>
-  </si>
-  <si>
-    <t>0.174</t>
-  </si>
-  <si>
-    <t>0.130</t>
-  </si>
-  <si>
-    <t>0.108</t>
-  </si>
-  <si>
-    <t>0.144</t>
-  </si>
-  <si>
-    <t>0.116</t>
-  </si>
-  <si>
-    <t>0.146</t>
-  </si>
-  <si>
-    <t>0.218</t>
-  </si>
-  <si>
-    <t>0.226</t>
-  </si>
-  <si>
-    <t>0.168</t>
-  </si>
-  <si>
-    <t>0.159</t>
-  </si>
-  <si>
-    <t>0.256</t>
-  </si>
-  <si>
-    <t>0.127</t>
-  </si>
-  <si>
-    <t>0.086</t>
-  </si>
-  <si>
-    <t>0.054</t>
-  </si>
-  <si>
-    <t>0.111</t>
-  </si>
-  <si>
-    <t>0.134</t>
-  </si>
-  <si>
-    <t>0.091</t>
-  </si>
-  <si>
-    <t>0.143</t>
-  </si>
-  <si>
-    <t>0.101</t>
-  </si>
-  <si>
-    <t>0.077</t>
-  </si>
-  <si>
-    <t>0.062</t>
-  </si>
-  <si>
-    <t>0.042</t>
-  </si>
-  <si>
-    <t>0.085</t>
-  </si>
-  <si>
-    <t>0.106</t>
-  </si>
-  <si>
-    <t>0.139</t>
-  </si>
-  <si>
-    <t>0.128</t>
-  </si>
-  <si>
-    <t>0.016</t>
-  </si>
-  <si>
-    <t>0.017</t>
-  </si>
-  <si>
-    <t>0.032</t>
-  </si>
-  <si>
-    <t>0.053</t>
-  </si>
-  <si>
-    <t>0.064</t>
-  </si>
-  <si>
-    <t>0.022</t>
-  </si>
-  <si>
-    <t>0.003</t>
+    <t>0.058</t>
+  </si>
+  <si>
+    <t>0.051</t>
+  </si>
+  <si>
+    <t>0.066</t>
+  </si>
+  <si>
+    <t>0.048</t>
+  </si>
+  <si>
+    <t>0.094</t>
+  </si>
+  <si>
+    <t>0.049</t>
+  </si>
+  <si>
+    <t>0.046</t>
   </si>
   <si>
     <t>0.015</t>
   </si>
   <si>
-    <t>0.000</t>
-  </si>
-  <si>
-    <t>0.007</t>
-  </si>
-  <si>
-    <t>0.014</t>
-  </si>
-  <si>
-    <t>0.040</t>
-  </si>
-  <si>
-    <t>0.033</t>
-  </si>
-  <si>
-    <t>0.035</t>
-  </si>
-  <si>
-    <t>0.098</t>
-  </si>
-  <si>
-    <t>0.069</t>
-  </si>
-  <si>
-    <t>0.131</t>
-  </si>
-  <si>
-    <t>0.072</t>
-  </si>
-  <si>
-    <t>0.247</t>
-  </si>
-  <si>
-    <t>0.265</t>
-  </si>
-  <si>
-    <t>0.211</t>
-  </si>
-  <si>
-    <t>0.253</t>
-  </si>
-  <si>
-    <t>0.254</t>
-  </si>
-  <si>
-    <t>0.047</t>
-  </si>
-  <si>
-    <t>0.057</t>
-  </si>
-  <si>
-    <t>0.458</t>
-  </si>
-  <si>
-    <t>0.510</t>
-  </si>
-  <si>
-    <t>0.555</t>
-  </si>
-  <si>
-    <t>0.717</t>
-  </si>
-  <si>
-    <t>0.688</t>
-  </si>
-  <si>
-    <t>0.025</t>
-  </si>
-  <si>
-    <t>0.041</t>
-  </si>
-  <si>
-    <t>0.095</t>
-  </si>
-  <si>
-    <t>0.070</t>
-  </si>
-  <si>
-    <t>0.110</t>
-  </si>
-  <si>
-    <t>0.157</t>
-  </si>
-  <si>
-    <t>0.105</t>
-  </si>
-  <si>
-    <t>0.186</t>
-  </si>
-  <si>
-    <t>0.151</t>
-  </si>
-  <si>
-    <t>0.100</t>
-  </si>
-  <si>
-    <t>0.192</t>
-  </si>
-  <si>
-    <t>0.102</t>
-  </si>
-  <si>
-    <t>0.051</t>
-  </si>
-  <si>
-    <t>0.164</t>
-  </si>
-  <si>
-    <t>0.058</t>
-  </si>
-  <si>
-    <t>0.066</t>
-  </si>
-  <si>
-    <t>0.048</t>
-  </si>
-  <si>
-    <t>0.094</t>
-  </si>
-  <si>
-    <t>0.049</t>
-  </si>
-  <si>
-    <t>0.046</t>
+    <t>0.020</t>
   </si>
   <si>
     <t>0.034</t>
@@ -579,67 +597,70 @@
     <t>0.037</t>
   </si>
   <si>
+    <t>0.076</t>
+  </si>
+  <si>
+    <t>0.089</t>
+  </si>
+  <si>
+    <t>0.397</t>
+  </si>
+  <si>
+    <t>0.156</t>
+  </si>
+  <si>
+    <t>0.060</t>
+  </si>
+  <si>
+    <t>0.237</t>
+  </si>
+  <si>
+    <t>0.246</t>
+  </si>
+  <si>
+    <t>0.286</t>
+  </si>
+  <si>
+    <t>0.296</t>
+  </si>
+  <si>
+    <t>0.272</t>
+  </si>
+  <si>
+    <t>0.084</t>
+  </si>
+  <si>
+    <t>0.083</t>
+  </si>
+  <si>
+    <t>0.560</t>
+  </si>
+  <si>
+    <t>0.517</t>
+  </si>
+  <si>
+    <t>0.556</t>
+  </si>
+  <si>
+    <t>0.731</t>
+  </si>
+  <si>
+    <t>0.740</t>
+  </si>
+  <si>
+    <t>0.087</t>
+  </si>
+  <si>
+    <t>0.124</t>
+  </si>
+  <si>
+    <t>0.183</t>
+  </si>
+  <si>
+    <t>0.181</t>
+  </si>
+  <si>
     <t>0.059</t>
-  </si>
-  <si>
-    <t>0.076</t>
-  </si>
-  <si>
-    <t>0.089</t>
-  </si>
-  <si>
-    <t>0.397</t>
-  </si>
-  <si>
-    <t>0.237</t>
-  </si>
-  <si>
-    <t>0.246</t>
-  </si>
-  <si>
-    <t>0.286</t>
-  </si>
-  <si>
-    <t>0.296</t>
-  </si>
-  <si>
-    <t>0.272</t>
-  </si>
-  <si>
-    <t>0.084</t>
-  </si>
-  <si>
-    <t>0.083</t>
-  </si>
-  <si>
-    <t>0.560</t>
-  </si>
-  <si>
-    <t>0.517</t>
-  </si>
-  <si>
-    <t>0.556</t>
-  </si>
-  <si>
-    <t>0.731</t>
-  </si>
-  <si>
-    <t>0.740</t>
-  </si>
-  <si>
-    <t>0.020</t>
-  </si>
-  <si>
-    <t>0.087</t>
-  </si>
-  <si>
-    <t>0.124</t>
-  </si>
-  <si>
-    <t>0.183</t>
-  </si>
-  <si>
-    <t>0.181</t>
   </si>
   <si>
     <t>0.162</t>
@@ -1009,7 +1030,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1037,87 +1058,87 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F2" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="B3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F3" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="B4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F4" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="B5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="E5" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F5" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="B6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E6" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F6" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1125,408 +1146,411 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E7" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="B8" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E8" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F8" t="s">
-        <v>104</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="B9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
         <v>16</v>
       </c>
-      <c r="C9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" t="s">
-        <v>63</v>
-      </c>
-      <c r="E9" t="s">
-        <v>80</v>
-      </c>
-      <c r="F9" t="s">
+      <c r="C10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" t="s">
+        <v>66</v>
+      </c>
+      <c r="E10" t="s">
+        <v>78</v>
+      </c>
+      <c r="F10" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="B11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" t="s">
+        <v>66</v>
+      </c>
+      <c r="E11" t="s">
+        <v>84</v>
+      </c>
+      <c r="F11" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" t="s">
+        <v>64</v>
+      </c>
+      <c r="E12" t="s">
+        <v>85</v>
+      </c>
+      <c r="F12" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" t="s">
+        <v>67</v>
+      </c>
+      <c r="E13" t="s">
+        <v>86</v>
+      </c>
+      <c r="F13" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14" t="s">
+        <v>68</v>
+      </c>
+      <c r="E14" t="s">
+        <v>87</v>
+      </c>
+      <c r="F14" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="B15" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="B10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" t="s">
-        <v>64</v>
-      </c>
-      <c r="E10" t="s">
-        <v>65</v>
-      </c>
-      <c r="F10" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" t="s">
-        <v>65</v>
-      </c>
-      <c r="E11" t="s">
-        <v>74</v>
-      </c>
-      <c r="F11" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="B12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" t="s">
-        <v>65</v>
-      </c>
-      <c r="E12" t="s">
-        <v>81</v>
-      </c>
-      <c r="F12" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" t="s">
-        <v>38</v>
-      </c>
-      <c r="D13" t="s">
-        <v>66</v>
-      </c>
-      <c r="E13" t="s">
-        <v>82</v>
-      </c>
-      <c r="F13" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="B14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" t="s">
-        <v>39</v>
-      </c>
-      <c r="D14" t="s">
-        <v>67</v>
-      </c>
-      <c r="E14" t="s">
-        <v>83</v>
-      </c>
-      <c r="F14" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" t="s">
-        <v>40</v>
-      </c>
-      <c r="D15" t="s">
-        <v>68</v>
-      </c>
       <c r="E15" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F15" t="s">
-        <v>65</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="B16" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D16" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="E16" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F16" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="B17" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C17" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D17" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="E17" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F17" t="s">
-        <v>46</v>
+        <v>113</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="B18" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D18" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E18" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="F18" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
     </row>
     <row r="19" spans="1:6">
+      <c r="A19" t="s">
+        <v>11</v>
+      </c>
       <c r="B19" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D19" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E19" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="F19" t="s">
-        <v>109</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" t="s">
-        <v>11</v>
-      </c>
       <c r="B20" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C20" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D20" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E20" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F20" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="B21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C21" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D21" t="s">
         <v>71</v>
       </c>
       <c r="E21" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F21" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="B22" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D22" t="s">
         <v>71</v>
       </c>
       <c r="E22" t="s">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="F22" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="B23" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" t="s">
+        <v>49</v>
+      </c>
+      <c r="D23" t="s">
+        <v>72</v>
+      </c>
+      <c r="E23" t="s">
+        <v>93</v>
+      </c>
+      <c r="F23" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" t="s">
+        <v>12</v>
+      </c>
+      <c r="B24" t="s">
         <v>25</v>
       </c>
-      <c r="C23" t="s">
-        <v>48</v>
-      </c>
-      <c r="D23" t="s">
-        <v>71</v>
-      </c>
-      <c r="E23" t="s">
-        <v>89</v>
-      </c>
-      <c r="F23" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="B24" t="s">
-        <v>17</v>
-      </c>
       <c r="C24" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D24" t="s">
+        <v>73</v>
+      </c>
+      <c r="E24" t="s">
+        <v>94</v>
+      </c>
+      <c r="F24" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="B25" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" t="s">
+        <v>51</v>
+      </c>
+      <c r="D25" t="s">
         <v>72</v>
       </c>
-      <c r="E24" t="s">
-        <v>90</v>
-      </c>
-      <c r="F24" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25" t="s">
-        <v>12</v>
-      </c>
-      <c r="B25" t="s">
-        <v>24</v>
-      </c>
-      <c r="C25" t="s">
-        <v>50</v>
-      </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
+        <v>95</v>
+      </c>
+      <c r="F25" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="A26" t="s">
+        <v>13</v>
+      </c>
+      <c r="B26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C26" t="s">
+        <v>52</v>
+      </c>
+      <c r="D26" t="s">
         <v>36</v>
       </c>
-      <c r="E25" t="s">
-        <v>91</v>
-      </c>
-      <c r="F25" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="B26" t="s">
-        <v>19</v>
-      </c>
-      <c r="C26" t="s">
-        <v>51</v>
-      </c>
-      <c r="D26" t="s">
-        <v>61</v>
-      </c>
       <c r="E26" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="F26" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="B27" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C27" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D27" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E27" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="F27" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C28" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D28" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E28" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F28" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="B29" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C29" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="D29" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E29" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F29" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -1534,87 +1558,104 @@
         <v>26</v>
       </c>
       <c r="C30" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="D30" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="E30" t="s">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="F30" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="B31" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C31" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D31" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="E31" t="s">
-        <v>96</v>
+        <v>66</v>
       </c>
       <c r="F31" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="B32" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" t="s">
+        <v>57</v>
+      </c>
+      <c r="D32" t="s">
+        <v>77</v>
+      </c>
+      <c r="E32" t="s">
+        <v>101</v>
+      </c>
+      <c r="F32" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
-      <c r="A32" t="s">
-        <v>13</v>
-      </c>
-      <c r="B32" t="s">
+    <row r="33" spans="1:6">
+      <c r="A33" t="s">
         <v>14</v>
       </c>
-      <c r="C32" t="s">
+      <c r="B33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C33" t="s">
         <v>36</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D33" t="s">
         <v>67</v>
       </c>
-      <c r="E32" t="s">
-        <v>97</v>
-      </c>
-      <c r="F32" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="33" spans="2:6">
-      <c r="B33" t="s">
-        <v>25</v>
-      </c>
-      <c r="C33" t="s">
+      <c r="E33" t="s">
+        <v>102</v>
+      </c>
+      <c r="F33" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="B34" t="s">
+        <v>26</v>
+      </c>
+      <c r="C34" t="s">
         <v>39</v>
       </c>
-      <c r="D33" t="s">
-        <v>73</v>
-      </c>
-      <c r="E33" t="s">
-        <v>76</v>
-      </c>
-      <c r="F33" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="34" spans="2:6">
-      <c r="B34" t="s">
-        <v>17</v>
-      </c>
-      <c r="C34" t="s">
-        <v>56</v>
-      </c>
       <c r="D34" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E34" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="F34" t="s">
-        <v>97</v>
+        <v>125</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="B35" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" t="s">
+        <v>58</v>
+      </c>
+      <c r="D35" t="s">
+        <v>78</v>
+      </c>
+      <c r="E35" t="s">
+        <v>103</v>
+      </c>
+      <c r="F35" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -1624,7 +1665,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1652,87 +1693,87 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D2" t="s">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="E2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="B3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="D3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="B4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D4" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F4" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="B5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
         <v>49</v>
       </c>
       <c r="D5" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E5" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F5" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="B6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D6" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E6" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F6" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1740,496 +1781,479 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="D7" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E7" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="B8" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="D8" t="s">
-        <v>140</v>
+        <v>37</v>
       </c>
       <c r="E8" t="s">
-        <v>104</v>
+        <v>150</v>
       </c>
       <c r="F8" t="s">
-        <v>164</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="B9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" t="s">
+        <v>129</v>
+      </c>
+      <c r="D9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
         <v>16</v>
       </c>
-      <c r="C9" t="s">
-        <v>124</v>
-      </c>
-      <c r="D9" t="s">
-        <v>141</v>
-      </c>
-      <c r="E9" t="s">
-        <v>129</v>
-      </c>
-      <c r="F9" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="B10" t="s">
-        <v>17</v>
-      </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="D10" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E10" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="F10" t="s">
-        <v>65</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" t="s">
-        <v>8</v>
-      </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E11" t="s">
+        <v>146</v>
+      </c>
+      <c r="F11" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" t="s">
+        <v>130</v>
+      </c>
+      <c r="D12" t="s">
+        <v>143</v>
+      </c>
+      <c r="E12" t="s">
         <v>81</v>
       </c>
-      <c r="F11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="B12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" t="s">
-        <v>61</v>
-      </c>
-      <c r="D12" t="s">
-        <v>65</v>
-      </c>
-      <c r="E12" t="s">
-        <v>140</v>
-      </c>
       <c r="F12" t="s">
-        <v>79</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" t="s">
-        <v>9</v>
-      </c>
       <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D13" t="s">
+        <v>68</v>
+      </c>
+      <c r="E13" t="s">
+        <v>151</v>
+      </c>
+      <c r="F13" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" t="s">
         <v>22</v>
       </c>
-      <c r="C13" t="s">
-        <v>125</v>
-      </c>
-      <c r="D13" t="s">
-        <v>142</v>
-      </c>
-      <c r="E13" t="s">
-        <v>77</v>
-      </c>
-      <c r="F13" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="B14" t="s">
-        <v>15</v>
-      </c>
       <c r="C14" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="D14" t="s">
         <v>68</v>
       </c>
       <c r="E14" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="F14" t="s">
-        <v>165</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" t="s">
-        <v>10</v>
-      </c>
       <c r="B15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C15" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" t="s">
+        <v>74</v>
+      </c>
+      <c r="E15" t="s">
+        <v>125</v>
+      </c>
+      <c r="F15" t="s">
         <v>42</v>
-      </c>
-      <c r="D15" t="s">
-        <v>68</v>
-      </c>
-      <c r="E15" t="s">
-        <v>149</v>
-      </c>
-      <c r="F15" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="B16" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>126</v>
+        <v>95</v>
       </c>
       <c r="D16" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="E16" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="F16" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="B17" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C17" t="s">
-        <v>127</v>
+        <v>45</v>
       </c>
       <c r="D17" t="s">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="E17" t="s">
-        <v>128</v>
+        <v>153</v>
       </c>
       <c r="F17" t="s">
-        <v>47</v>
+        <v>169</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="B18" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C18" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D18" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E18" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="F18" t="s">
-        <v>166</v>
+        <v>124</v>
       </c>
     </row>
     <row r="19" spans="1:6">
+      <c r="A19" t="s">
+        <v>11</v>
+      </c>
       <c r="B19" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>48</v>
+        <v>131</v>
       </c>
       <c r="D19" t="s">
-        <v>81</v>
+        <v>144</v>
       </c>
       <c r="E19" t="s">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="F19" t="s">
-        <v>120</v>
+        <v>170</v>
       </c>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" t="s">
-        <v>11</v>
-      </c>
       <c r="B20" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C20" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D20" t="s">
-        <v>143</v>
+        <v>69</v>
       </c>
       <c r="E20" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F20" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="B21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C21" t="s">
-        <v>129</v>
+        <v>39</v>
       </c>
       <c r="D21" t="s">
-        <v>62</v>
+        <v>144</v>
       </c>
       <c r="E21" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F21" t="s">
-        <v>168</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="B22" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>39</v>
+        <v>109</v>
       </c>
       <c r="D22" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E22" t="s">
-        <v>65</v>
+        <v>155</v>
       </c>
       <c r="F22" t="s">
-        <v>45</v>
+        <v>130</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="B23" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" t="s">
+        <v>103</v>
+      </c>
+      <c r="D23" t="s">
+        <v>145</v>
+      </c>
+      <c r="E23" t="s">
+        <v>92</v>
+      </c>
+      <c r="F23" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24" t="s">
         <v>25</v>
       </c>
-      <c r="C23" t="s">
-        <v>105</v>
-      </c>
-      <c r="D23" t="s">
-        <v>143</v>
-      </c>
-      <c r="E23" t="s">
-        <v>152</v>
-      </c>
-      <c r="F23" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="B24" t="s">
-        <v>17</v>
-      </c>
       <c r="C24" t="s">
-        <v>98</v>
+        <v>133</v>
       </c>
       <c r="D24" t="s">
-        <v>144</v>
+        <v>65</v>
       </c>
       <c r="E24" t="s">
-        <v>89</v>
+        <v>156</v>
       </c>
       <c r="F24" t="s">
-        <v>125</v>
+        <v>172</v>
       </c>
     </row>
     <row r="25" spans="1:6">
-      <c r="A25" t="s">
-        <v>12</v>
-      </c>
       <c r="B25" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C25" t="s">
-        <v>34</v>
+        <v>110</v>
       </c>
       <c r="D25" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E25" t="s">
-        <v>153</v>
+        <v>31</v>
       </c>
       <c r="F25" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="B26" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C26" t="s">
-        <v>106</v>
+        <v>134</v>
       </c>
       <c r="D26" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E26" t="s">
-        <v>30</v>
+        <v>157</v>
       </c>
       <c r="F26" t="s">
-        <v>170</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="B27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C27" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D27" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E27" t="s">
-        <v>154</v>
+        <v>31</v>
       </c>
       <c r="F27" t="s">
-        <v>126</v>
+        <v>174</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C28" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="D28" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="E28" t="s">
-        <v>30</v>
+        <v>158</v>
       </c>
       <c r="F28" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="B29" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C29" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="D29" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="E29" t="s">
-        <v>155</v>
+        <v>66</v>
       </c>
       <c r="F29" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" t="s">
+        <v>116</v>
+      </c>
+      <c r="D30" t="s">
+        <v>65</v>
+      </c>
+      <c r="E30" t="s">
+        <v>159</v>
+      </c>
+      <c r="F30" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" t="s">
+        <v>14</v>
+      </c>
+      <c r="B31" t="s">
+        <v>15</v>
+      </c>
+      <c r="C31" t="s">
+        <v>65</v>
+      </c>
+      <c r="D31" t="s">
+        <v>68</v>
+      </c>
+      <c r="E31" t="s">
+        <v>160</v>
+      </c>
+      <c r="F31" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="B32" t="s">
         <v>26</v>
       </c>
-      <c r="C30" t="s">
-        <v>133</v>
-      </c>
-      <c r="D30" t="s">
-        <v>71</v>
-      </c>
-      <c r="E30" t="s">
-        <v>65</v>
-      </c>
-      <c r="F30" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="B31" t="s">
-        <v>17</v>
-      </c>
-      <c r="C31" t="s">
-        <v>112</v>
-      </c>
-      <c r="D31" t="s">
-        <v>70</v>
-      </c>
-      <c r="E31" t="s">
-        <v>156</v>
-      </c>
-      <c r="F31" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32" t="s">
-        <v>13</v>
-      </c>
-      <c r="B32" t="s">
-        <v>14</v>
-      </c>
       <c r="C32" t="s">
-        <v>70</v>
+        <v>138</v>
       </c>
       <c r="D32" t="s">
-        <v>68</v>
+        <v>146</v>
       </c>
       <c r="E32" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="F32" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C33" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="D33" t="s">
-        <v>140</v>
+        <v>67</v>
       </c>
       <c r="E33" t="s">
-        <v>158</v>
+        <v>80</v>
       </c>
       <c r="F33" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="34" spans="2:6">
-      <c r="B34" t="s">
-        <v>17</v>
-      </c>
-      <c r="C34" t="s">
-        <v>135</v>
-      </c>
-      <c r="D34" t="s">
-        <v>67</v>
-      </c>
-      <c r="E34" t="s">
-        <v>76</v>
-      </c>
-      <c r="F34" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -2239,7 +2263,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -2267,87 +2291,87 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>173</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F2" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="B3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="D3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="E3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F3" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="B4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E4" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="F4" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="B5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E5" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F5" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="B6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E6" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="F6" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -2355,408 +2379,411 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>127</v>
+        <v>154</v>
       </c>
       <c r="D7" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E7" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="F7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="B8" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>175</v>
+        <v>95</v>
       </c>
       <c r="D8" t="s">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="E8" t="s">
-        <v>78</v>
+        <v>184</v>
       </c>
       <c r="F8" t="s">
-        <v>104</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="B9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
         <v>16</v>
       </c>
-      <c r="C9" t="s">
-        <v>127</v>
-      </c>
-      <c r="D9" t="s">
-        <v>144</v>
-      </c>
-      <c r="E9" t="s">
-        <v>187</v>
-      </c>
-      <c r="F9" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="B10" t="s">
-        <v>17</v>
-      </c>
       <c r="C10" t="s">
-        <v>176</v>
+        <v>69</v>
       </c>
       <c r="D10" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E10" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="F10" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" t="s">
-        <v>8</v>
-      </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C11" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E11" t="s">
-        <v>62</v>
+        <v>146</v>
       </c>
       <c r="F11" t="s">
-        <v>56</v>
+        <v>189</v>
       </c>
     </row>
     <row r="12" spans="1:6">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" t="s">
+        <v>143</v>
+      </c>
+      <c r="E12" t="s">
+        <v>193</v>
+      </c>
+      <c r="F12" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="s">
+        <v>142</v>
+      </c>
+      <c r="D13" t="s">
         <v>68</v>
       </c>
-      <c r="D12" t="s">
-        <v>65</v>
-      </c>
-      <c r="E12" t="s">
-        <v>140</v>
-      </c>
-      <c r="F12" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="E13" t="s">
+        <v>185</v>
+      </c>
+      <c r="F13" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" t="s">
         <v>22</v>
       </c>
-      <c r="C13" t="s">
-        <v>40</v>
-      </c>
-      <c r="D13" t="s">
-        <v>142</v>
-      </c>
-      <c r="E13" t="s">
-        <v>188</v>
-      </c>
-      <c r="F13" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="B14" t="s">
-        <v>15</v>
-      </c>
       <c r="C14" t="s">
-        <v>139</v>
+        <v>173</v>
       </c>
       <c r="D14" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E14" t="s">
-        <v>181</v>
+        <v>89</v>
       </c>
       <c r="F14" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" t="s">
-        <v>10</v>
-      </c>
       <c r="B15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="D15" t="s">
-        <v>66</v>
+        <v>146</v>
       </c>
       <c r="E15" t="s">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="F15" t="s">
-        <v>65</v>
+        <v>152</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="B16" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C16" t="s">
-        <v>177</v>
+        <v>80</v>
       </c>
       <c r="D16" t="s">
-        <v>140</v>
+        <v>69</v>
       </c>
       <c r="E16" t="s">
-        <v>121</v>
+        <v>152</v>
       </c>
       <c r="F16" t="s">
-        <v>149</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="B17" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C17" t="s">
-        <v>76</v>
+        <v>123</v>
       </c>
       <c r="D17" t="s">
-        <v>62</v>
+        <v>188</v>
       </c>
       <c r="E17" t="s">
-        <v>149</v>
+        <v>110</v>
       </c>
       <c r="F17" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="B18" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C18" t="s">
-        <v>119</v>
+        <v>48</v>
       </c>
       <c r="D18" t="s">
-        <v>141</v>
+        <v>37</v>
       </c>
       <c r="E18" t="s">
-        <v>106</v>
+        <v>194</v>
       </c>
       <c r="F18" t="s">
-        <v>110</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:6">
+      <c r="A19" t="s">
+        <v>11</v>
+      </c>
       <c r="B19" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>48</v>
+        <v>179</v>
       </c>
       <c r="D19" t="s">
-        <v>37</v>
+        <v>144</v>
       </c>
       <c r="E19" t="s">
-        <v>189</v>
+        <v>66</v>
       </c>
       <c r="F19" t="s">
-        <v>110</v>
+        <v>170</v>
       </c>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" t="s">
-        <v>11</v>
-      </c>
       <c r="B20" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C20" t="s">
-        <v>78</v>
+        <v>180</v>
       </c>
       <c r="D20" t="s">
-        <v>143</v>
+        <v>71</v>
       </c>
       <c r="E20" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F20" t="s">
-        <v>167</v>
+        <v>211</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="B21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C21" t="s">
-        <v>104</v>
+        <v>180</v>
       </c>
       <c r="D21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E21" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F21" t="s">
-        <v>205</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="B22" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C22" t="s">
-        <v>104</v>
+        <v>181</v>
       </c>
       <c r="D22" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E22" t="s">
-        <v>65</v>
+        <v>195</v>
       </c>
       <c r="F22" t="s">
-        <v>49</v>
+        <v>212</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="B23" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" t="s">
+        <v>182</v>
+      </c>
+      <c r="D23" t="s">
+        <v>36</v>
+      </c>
+      <c r="E23" t="s">
+        <v>93</v>
+      </c>
+      <c r="F23" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" t="s">
+        <v>12</v>
+      </c>
+      <c r="B24" t="s">
         <v>25</v>
       </c>
-      <c r="C23" t="s">
-        <v>178</v>
-      </c>
-      <c r="D23" t="s">
-        <v>73</v>
-      </c>
-      <c r="E23" t="s">
-        <v>190</v>
-      </c>
-      <c r="F23" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="B24" t="s">
-        <v>17</v>
-      </c>
       <c r="C24" t="s">
-        <v>176</v>
+        <v>58</v>
       </c>
       <c r="D24" t="s">
-        <v>36</v>
+        <v>138</v>
       </c>
       <c r="E24" t="s">
-        <v>90</v>
+        <v>196</v>
       </c>
       <c r="F24" t="s">
-        <v>207</v>
+        <v>111</v>
       </c>
     </row>
     <row r="25" spans="1:6">
-      <c r="A25" t="s">
-        <v>12</v>
-      </c>
       <c r="B25" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C25" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="D25" t="s">
-        <v>139</v>
+        <v>189</v>
       </c>
       <c r="E25" t="s">
-        <v>28</v>
+        <v>197</v>
       </c>
       <c r="F25" t="s">
-        <v>30</v>
+        <v>214</v>
       </c>
     </row>
     <row r="26" spans="1:6">
+      <c r="A26" t="s">
+        <v>13</v>
+      </c>
       <c r="B26" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C26" t="s">
-        <v>179</v>
+        <v>131</v>
       </c>
       <c r="D26" t="s">
-        <v>61</v>
+        <v>142</v>
       </c>
       <c r="E26" t="s">
-        <v>191</v>
+        <v>29</v>
       </c>
       <c r="F26" t="s">
-        <v>208</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="B27" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C27" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D27" t="s">
-        <v>135</v>
+        <v>74</v>
       </c>
       <c r="E27" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="F27" t="s">
-        <v>49</v>
+        <v>215</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C28" t="s">
-        <v>46</v>
+        <v>184</v>
       </c>
       <c r="D28" t="s">
-        <v>81</v>
+        <v>139</v>
       </c>
       <c r="E28" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="F28" t="s">
-        <v>209</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="B29" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C29" t="s">
-        <v>181</v>
+        <v>46</v>
       </c>
       <c r="D29" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E29" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="F29" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -2764,87 +2791,104 @@
         <v>26</v>
       </c>
       <c r="C30" t="s">
-        <v>123</v>
+        <v>185</v>
       </c>
       <c r="D30" t="s">
-        <v>140</v>
+        <v>84</v>
       </c>
       <c r="E30" t="s">
-        <v>65</v>
+        <v>201</v>
       </c>
       <c r="F30" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="B31" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C31" t="s">
-        <v>77</v>
+        <v>127</v>
       </c>
       <c r="D31" t="s">
-        <v>73</v>
+        <v>146</v>
       </c>
       <c r="E31" t="s">
-        <v>195</v>
+        <v>66</v>
       </c>
       <c r="F31" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="B32" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" t="s">
+        <v>81</v>
+      </c>
+      <c r="D32" t="s">
+        <v>75</v>
+      </c>
+      <c r="E32" t="s">
+        <v>202</v>
+      </c>
+      <c r="F32" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" t="s">
+        <v>14</v>
+      </c>
+      <c r="B33" t="s">
+        <v>15</v>
+      </c>
+      <c r="C33" t="s">
+        <v>75</v>
+      </c>
+      <c r="D33" t="s">
+        <v>146</v>
+      </c>
+      <c r="E33" t="s">
+        <v>109</v>
+      </c>
+      <c r="F33" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="B34" t="s">
+        <v>26</v>
+      </c>
+      <c r="C34" t="s">
+        <v>65</v>
+      </c>
+      <c r="D34" t="s">
+        <v>74</v>
+      </c>
+      <c r="E34" t="s">
+        <v>203</v>
+      </c>
+      <c r="F34" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
-      <c r="A32" t="s">
-        <v>13</v>
-      </c>
-      <c r="B32" t="s">
-        <v>14</v>
-      </c>
-      <c r="C32" t="s">
-        <v>73</v>
-      </c>
-      <c r="D32" t="s">
-        <v>140</v>
-      </c>
-      <c r="E32" t="s">
-        <v>105</v>
-      </c>
-      <c r="F32" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="33" spans="2:6">
-      <c r="B33" t="s">
-        <v>25</v>
-      </c>
-      <c r="C33" t="s">
-        <v>70</v>
-      </c>
-      <c r="D33" t="s">
-        <v>61</v>
-      </c>
-      <c r="E33" t="s">
-        <v>196</v>
-      </c>
-      <c r="F33" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="34" spans="2:6">
-      <c r="B34" t="s">
-        <v>17</v>
-      </c>
-      <c r="C34" t="s">
-        <v>70</v>
-      </c>
-      <c r="D34" t="s">
-        <v>62</v>
-      </c>
-      <c r="E34" t="s">
-        <v>197</v>
-      </c>
-      <c r="F34" t="s">
-        <v>128</v>
+    <row r="35" spans="1:6">
+      <c r="B35" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" t="s">
+        <v>65</v>
+      </c>
+      <c r="D35" t="s">
+        <v>69</v>
+      </c>
+      <c r="E35" t="s">
+        <v>204</v>
+      </c>
+      <c r="F35" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>
